--- a/artfynd/S 2985-2024 artfynd.xlsx
+++ b/artfynd/S 2985-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16986131</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16990274</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1041,6 +1056,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16990275</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1167,6 +1187,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16990276</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1284,6 +1309,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16989579</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1401,6 +1431,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16989580</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1518,6 +1553,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16989581</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1635,6 +1675,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16989582</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1752,6 +1797,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16989583</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1869,6 +1919,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16989584</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1986,6 +2041,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16989585</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2103,6 +2163,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16989586</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2220,6 +2285,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16989587</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2337,6 +2407,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16989588</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2454,6 +2529,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16989589</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2571,6 +2651,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16989590</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2688,6 +2773,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16989591</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2814,6 +2904,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16990077</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2931,6 +3026,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16985624</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3048,6 +3148,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16985625</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3165,6 +3270,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16986114</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3282,6 +3392,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16986115</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3399,6 +3514,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16986116</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3516,6 +3636,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16986117</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3633,6 +3758,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16986118</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3750,6 +3880,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16986119</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3867,6 +4002,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16986120</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3984,6 +4124,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16986121</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4101,6 +4246,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16986122</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4218,6 +4368,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16986123</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4335,6 +4490,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16986124</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4452,6 +4612,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16986125</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4578,6 +4743,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16990055</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4704,6 +4874,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16990056</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4830,6 +5005,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16990057</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4956,6 +5136,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16990058</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5082,6 +5267,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16990059</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5208,6 +5398,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16990060</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5334,6 +5529,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16990061</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5460,6 +5660,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16990062</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5586,6 +5791,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16990063</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5712,6 +5922,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16990064</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5838,6 +6053,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16990065</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5964,6 +6184,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16990066</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6090,6 +6315,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16990067</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6216,8 +6446,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16990069</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>